--- a/dataset_t6_grouped/results2/G4/G4_T6321_W0022F0001T0006Z000C1N65_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T6321_W0022F0001T0006Z000C1N65_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>44.45201685965495</v>
+        <v>7.22345273969393</v>
       </c>
       <c r="D2" t="n">
-        <v>44.93183218240356</v>
+        <v>7.301422729640579</v>
       </c>
       <c r="E2" t="n">
-        <v>1.627102089567527</v>
+        <v>0.2644040895547234</v>
       </c>
       <c r="F2" t="n">
-        <v>1.702105609442677</v>
+        <v>0.2765921615344349</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>48.30081558957939</v>
+        <v>7.848882533306651</v>
       </c>
       <c r="D3" t="n">
-        <v>48.59729726896899</v>
+        <v>7.897060806207461</v>
       </c>
       <c r="E3" t="n">
-        <v>1.627102089567527</v>
+        <v>0.2644040895547234</v>
       </c>
       <c r="F3" t="n">
-        <v>1.702105609442677</v>
+        <v>0.2765921615344349</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>45.47995836345658</v>
+        <v>7.390493234061695</v>
       </c>
       <c r="D4" t="n">
-        <v>45.04395144838936</v>
+        <v>7.319642110363272</v>
       </c>
       <c r="E4" t="n">
-        <v>1.627102089567527</v>
+        <v>0.2644040895547234</v>
       </c>
       <c r="F4" t="n">
-        <v>1.702105609442677</v>
+        <v>0.2765921615344349</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
